--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2704A86-BF7B-4C73-BDF4-A433010F241F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB7CAD8-F8F1-4C3C-99B7-2CAFF1F53D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="CQSD" sheetId="2" r:id="rId2"/>
-    <sheet name="RQSD" sheetId="3" r:id="rId3"/>
+    <sheet name="RQSD-BRQSD" sheetId="2" r:id="rId2"/>
+    <sheet name="RQSD-RQSD" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,9 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
   <si>
     <t>Source:</t>
+  </si>
+  <si>
+    <t>Each U.S. state that has an RPS defines the sources that qualify for that RPS, leading to</t>
   </si>
   <si>
     <t>nuclear</t>
@@ -66,6 +69,9 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>The non-BAU version of this variable supports a boolean policy lever and is intended to be set by the</t>
+  </si>
+  <si>
     <t>RQSD BAU RPS Qualifying Source Definitions</t>
   </si>
   <si>
@@ -82,6 +88,27 @@
   </si>
   <si>
     <t>offshore wind</t>
+  </si>
+  <si>
+    <t>differences between states.  Here, we use a "clean energy standard"</t>
+  </si>
+  <si>
+    <t>(counting everything except fossil fuels) as our definition for the BAU case.</t>
+  </si>
+  <si>
+    <t>model user.  The example we include uses only wind, solar, and geothermal.</t>
+  </si>
+  <si>
+    <t>Hydro is excluded because of limited potential for new large hydro and land use impacts.</t>
+  </si>
+  <si>
+    <t>Biomass is excluded because it is not truly carbon-neutral, and it has other issues, such as</t>
+  </si>
+  <si>
+    <t>local air quality impacts and land use challenges.</t>
+  </si>
+  <si>
+    <t>Nuclear is excluded because of the need to manage nuclear waste.</t>
   </si>
   <si>
     <t>see notes</t>
@@ -124,18 +151,6 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
-  </si>
-  <si>
-    <t>Here we define the resources that qualify for both a renewable portfolio standard (RPS) and a clean electricity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">standard (CES). </t>
-  </si>
-  <si>
-    <t>These definitions can vary by U.S. state, but we primarily utilize the CES (counting everything except fossil fuels)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">for the U.S national model. </t>
   </si>
 </sst>
 </file>
@@ -195,7 +210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -205,7 +220,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -511,60 +525,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="84.54296875" customWidth="1"/>
+    <col min="2" max="2" width="84.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="2"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B5" s="2"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -578,15 +614,15 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B1" s="3">
         <v>2021</v>
@@ -679,9 +715,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -774,9 +810,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -869,9 +905,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -964,9 +1000,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1059,9 +1095,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1154,674 +1190,674 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
+      </c>
+      <c r="AE10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>1</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>14</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7">
-        <v>1</v>
-      </c>
-      <c r="V7">
-        <v>1</v>
-      </c>
-      <c r="W7">
-        <v>1</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>1</v>
-      </c>
-      <c r="Z7">
-        <v>1</v>
-      </c>
-      <c r="AA7">
-        <v>1</v>
-      </c>
-      <c r="AB7">
-        <v>1</v>
-      </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AD7">
-        <v>1</v>
-      </c>
-      <c r="AE7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="V8">
-        <v>1</v>
-      </c>
-      <c r="W8">
-        <v>1</v>
-      </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8">
-        <v>1</v>
-      </c>
-      <c r="Z8">
-        <v>1</v>
-      </c>
-      <c r="AA8">
-        <v>1</v>
-      </c>
-      <c r="AB8">
-        <v>1</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AD8">
-        <v>1</v>
-      </c>
-      <c r="AE8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9">
-        <v>1</v>
-      </c>
-      <c r="T9">
-        <v>1</v>
-      </c>
-      <c r="U9">
-        <v>1</v>
-      </c>
-      <c r="V9">
-        <v>1</v>
-      </c>
-      <c r="W9">
-        <v>1</v>
-      </c>
-      <c r="X9">
-        <v>1</v>
-      </c>
-      <c r="Y9">
-        <v>1</v>
-      </c>
-      <c r="Z9">
-        <v>1</v>
-      </c>
-      <c r="AA9">
-        <v>1</v>
-      </c>
-      <c r="AB9">
-        <v>1</v>
-      </c>
-      <c r="AC9">
-        <v>1</v>
-      </c>
-      <c r="AD9">
-        <v>1</v>
-      </c>
-      <c r="AE9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-      <c r="P10">
-        <v>1</v>
-      </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
-      <c r="R10">
-        <v>1</v>
-      </c>
-      <c r="S10">
-        <v>1</v>
-      </c>
-      <c r="T10">
-        <v>1</v>
-      </c>
-      <c r="U10">
-        <v>1</v>
-      </c>
-      <c r="V10">
-        <v>1</v>
-      </c>
-      <c r="W10">
-        <v>1</v>
-      </c>
-      <c r="X10">
-        <v>1</v>
-      </c>
-      <c r="Y10">
-        <v>1</v>
-      </c>
-      <c r="Z10">
-        <v>1</v>
-      </c>
-      <c r="AA10">
-        <v>1</v>
-      </c>
-      <c r="AB10">
-        <v>1</v>
-      </c>
-      <c r="AC10">
-        <v>1</v>
-      </c>
-      <c r="AD10">
-        <v>1</v>
-      </c>
-      <c r="AE10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11">
-        <v>1</v>
-      </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <v>1</v>
-      </c>
-      <c r="T11">
-        <v>1</v>
-      </c>
-      <c r="U11">
-        <v>1</v>
-      </c>
-      <c r="V11">
-        <v>1</v>
-      </c>
-      <c r="W11">
-        <v>1</v>
-      </c>
-      <c r="X11">
-        <v>1</v>
-      </c>
-      <c r="Y11">
-        <v>1</v>
-      </c>
-      <c r="Z11">
-        <v>1</v>
-      </c>
-      <c r="AA11">
-        <v>1</v>
-      </c>
-      <c r="AB11">
-        <v>1</v>
-      </c>
-      <c r="AC11">
-        <v>1</v>
-      </c>
-      <c r="AD11">
-        <v>1</v>
-      </c>
-      <c r="AE11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>12</v>
       </c>
       <c r="B14">
         <f>B2</f>
@@ -1944,9 +1980,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -2039,9 +2075,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2134,9 +2170,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2229,9 +2265,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2324,9 +2360,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -2419,9 +2455,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -2514,9 +2550,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -2609,9 +2645,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -2704,9 +2740,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -2799,9 +2835,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -2894,9 +2930,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -3000,15 +3036,15 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B1" s="3">
         <v>2021</v>
@@ -3101,9 +3137,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3196,9 +3232,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3291,9 +3327,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3386,9 +3422,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3481,9 +3517,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3576,674 +3612,674 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>1</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>14</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7">
-        <v>1</v>
-      </c>
-      <c r="V7">
-        <v>1</v>
-      </c>
-      <c r="W7">
-        <v>1</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>1</v>
-      </c>
-      <c r="Z7">
-        <v>1</v>
-      </c>
-      <c r="AA7">
-        <v>1</v>
-      </c>
-      <c r="AB7">
-        <v>1</v>
-      </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AD7">
-        <v>1</v>
-      </c>
-      <c r="AE7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="V8">
-        <v>1</v>
-      </c>
-      <c r="W8">
-        <v>1</v>
-      </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8">
-        <v>1</v>
-      </c>
-      <c r="Z8">
-        <v>1</v>
-      </c>
-      <c r="AA8">
-        <v>1</v>
-      </c>
-      <c r="AB8">
-        <v>1</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AD8">
-        <v>1</v>
-      </c>
-      <c r="AE8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9">
-        <v>1</v>
-      </c>
-      <c r="T9">
-        <v>1</v>
-      </c>
-      <c r="U9">
-        <v>1</v>
-      </c>
-      <c r="V9">
-        <v>1</v>
-      </c>
-      <c r="W9">
-        <v>1</v>
-      </c>
-      <c r="X9">
-        <v>1</v>
-      </c>
-      <c r="Y9">
-        <v>1</v>
-      </c>
-      <c r="Z9">
-        <v>1</v>
-      </c>
-      <c r="AA9">
-        <v>1</v>
-      </c>
-      <c r="AB9">
-        <v>1</v>
-      </c>
-      <c r="AC9">
-        <v>1</v>
-      </c>
-      <c r="AD9">
-        <v>1</v>
-      </c>
-      <c r="AE9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11">
-        <v>1</v>
-      </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <v>1</v>
-      </c>
-      <c r="T11">
-        <v>1</v>
-      </c>
-      <c r="U11">
-        <v>1</v>
-      </c>
-      <c r="V11">
-        <v>1</v>
-      </c>
-      <c r="W11">
-        <v>1</v>
-      </c>
-      <c r="X11">
-        <v>1</v>
-      </c>
-      <c r="Y11">
-        <v>1</v>
-      </c>
-      <c r="Z11">
-        <v>1</v>
-      </c>
-      <c r="AA11">
-        <v>1</v>
-      </c>
-      <c r="AB11">
-        <v>1</v>
-      </c>
-      <c r="AC11">
-        <v>1</v>
-      </c>
-      <c r="AD11">
-        <v>1</v>
-      </c>
-      <c r="AE11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>12</v>
       </c>
       <c r="B14">
         <f>B2</f>
@@ -4366,9 +4402,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -4461,9 +4497,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4556,9 +4592,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -4651,9 +4687,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -4746,9 +4782,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -4841,9 +4877,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4936,9 +4972,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -5031,9 +5067,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -5126,9 +5162,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -5221,9 +5257,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -5316,9 +5352,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B25">
         <v>1</v>

--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB7CAD8-F8F1-4C3C-99B7-2CAFF1F53D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B661A6-F510-434A-B3E0-7371A419171D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9120" yWindow="690" windowWidth="19110" windowHeight="16425" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="RQSD-BRQSD" sheetId="2" r:id="rId2"/>
+    <sheet name="RQSD-CQSD" sheetId="2" r:id="rId2"/>
     <sheet name="RQSD-RQSD" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -34,12 +34,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>Source:</t>
-  </si>
-  <si>
-    <t>Each U.S. state that has an RPS defines the sources that qualify for that RPS, leading to</t>
   </si>
   <si>
     <t>nuclear</t>
@@ -69,9 +66,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>The non-BAU version of this variable supports a boolean policy lever and is intended to be set by the</t>
-  </si>
-  <si>
     <t>RQSD BAU RPS Qualifying Source Definitions</t>
   </si>
   <si>
@@ -88,27 +82,6 @@
   </si>
   <si>
     <t>offshore wind</t>
-  </si>
-  <si>
-    <t>differences between states.  Here, we use a "clean energy standard"</t>
-  </si>
-  <si>
-    <t>(counting everything except fossil fuels) as our definition for the BAU case.</t>
-  </si>
-  <si>
-    <t>model user.  The example we include uses only wind, solar, and geothermal.</t>
-  </si>
-  <si>
-    <t>Hydro is excluded because of limited potential for new large hydro and land use impacts.</t>
-  </si>
-  <si>
-    <t>Biomass is excluded because it is not truly carbon-neutral, and it has other issues, such as</t>
-  </si>
-  <si>
-    <t>local air quality impacts and land use challenges.</t>
-  </si>
-  <si>
-    <t>Nuclear is excluded because of the need to manage nuclear waste.</t>
   </si>
   <si>
     <t>see notes</t>
@@ -151,6 +124,18 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
+  </si>
+  <si>
+    <t>Here we define the resources that qualify for both a renewable portfolio standard (RPS) and a clean electricity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">standard (CES). </t>
+  </si>
+  <si>
+    <t>These definitions can vary by U.S. state, but we primarily utilize the CES (counting everything except fossil fuels)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for the U.S national model. </t>
   </si>
 </sst>
 </file>
@@ -525,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="84.5703125" customWidth="1"/>
@@ -533,12 +518,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -546,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -554,53 +539,31 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
+      <c r="A13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -622,7 +585,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B1" s="3">
         <v>2021</v>
@@ -717,7 +680,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -812,7 +775,7 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -907,7 +870,7 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1002,7 +965,7 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1097,7 +1060,7 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1192,7 +1155,7 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1287,7 +1250,7 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1382,7 +1345,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1477,7 +1440,7 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1572,7 +1535,7 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1667,7 +1630,7 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1762,7 +1725,7 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1857,7 +1820,7 @@
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <f>B2</f>
@@ -1982,7 +1945,7 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -2077,7 +2040,7 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2172,7 +2135,7 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2267,7 +2230,7 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2362,7 +2325,7 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -2457,7 +2420,7 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -2552,7 +2515,7 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -2647,7 +2610,7 @@
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -2742,7 +2705,7 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -2837,7 +2800,7 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -2932,7 +2895,7 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -3044,7 +3007,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B1" s="3">
         <v>2021</v>
@@ -3139,7 +3102,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3234,7 +3197,7 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3329,7 +3292,7 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3424,7 +3387,7 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3519,7 +3482,7 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3614,7 +3577,7 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -3709,7 +3672,7 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -3804,7 +3767,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -3899,7 +3862,7 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3994,7 +3957,7 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -4089,7 +4052,7 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4184,7 +4147,7 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4279,7 +4242,7 @@
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <f>B2</f>
@@ -4404,7 +4367,7 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -4499,7 +4462,7 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4594,7 +4557,7 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -4689,7 +4652,7 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -4784,7 +4747,7 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -4879,7 +4842,7 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4974,7 +4937,7 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -5069,7 +5032,7 @@
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -5164,7 +5127,7 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -5259,7 +5222,7 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -5354,7 +5317,7 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B25">
         <v>1</v>
